--- a/backend/data/financials_by_company/002208.SZ.xlsx
+++ b/backend/data/financials_by_company/002208.SZ.xlsx
@@ -677,622 +677,622 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>-68919534.8175</v>
+        <v>-11962454.652747</v>
       </c>
       <c r="C2" t="n">
-        <v>0.25</v>
+        <v>0.200048</v>
       </c>
       <c r="D2" t="n">
-        <v>890149421.4</v>
+        <v>1394202701.3</v>
       </c>
       <c r="E2" t="n">
-        <v>-275678139.27</v>
+        <v>-59797989.03</v>
       </c>
       <c r="F2" t="n">
-        <v>-275678139.27</v>
+        <v>-59797989.03</v>
       </c>
       <c r="G2" t="n">
-        <v>-56572549.96</v>
+        <v>876920607.1799999</v>
       </c>
       <c r="H2" t="n">
-        <v>77917320.40000001</v>
+        <v>38114253.65</v>
       </c>
       <c r="I2" t="n">
-        <v>6490627875.1</v>
+        <v>5420825812.91</v>
       </c>
       <c r="J2" t="n">
-        <v>614471282.13</v>
+        <v>1334404712.27</v>
       </c>
       <c r="K2" t="n">
-        <v>536553961.73</v>
+        <v>1296290458.62</v>
       </c>
       <c r="L2" t="n">
-        <v>-8564285.98</v>
+        <v>-1000476.2</v>
       </c>
       <c r="M2" t="n">
-        <v>239792042.3</v>
+        <v>170949945.78</v>
       </c>
       <c r="N2" t="n">
-        <v>64167677.7</v>
+        <v>68496874.36</v>
       </c>
       <c r="O2" t="n">
-        <v>150186054.4925</v>
+        <v>924756141.557253</v>
       </c>
       <c r="P2" t="n">
-        <v>-56572549.96</v>
+        <v>876920607.1799999</v>
       </c>
       <c r="Q2" t="n">
-        <v>6930995940.92</v>
+        <v>6272212889.8</v>
       </c>
       <c r="R2" t="n">
-        <v>295123670.3</v>
+        <v>1123096385.03</v>
       </c>
       <c r="S2" t="n">
-        <v>808179285</v>
+        <v>804514319</v>
       </c>
       <c r="T2" t="n">
-        <v>808179285</v>
+        <v>804514319</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.07000000000000001</v>
+        <v>1.09</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.07000000000000001</v>
+        <v>1.09</v>
       </c>
       <c r="W2" t="n">
-        <v>-56572549.96</v>
+        <v>876920607.1799999</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>-56572549.96</v>
+        <v>876920607.1799999</v>
       </c>
       <c r="Z2" t="n">
-        <v>-152246600.38</v>
+        <v>-23298039.99</v>
       </c>
       <c r="AA2" t="n">
-        <v>95674050.42</v>
+        <v>900218647.17</v>
       </c>
       <c r="AB2" t="n">
-        <v>95674050.42</v>
+        <v>900218647.17</v>
       </c>
       <c r="AC2" t="n">
-        <v>201087869.01</v>
+        <v>225121865.67</v>
       </c>
       <c r="AD2" t="n">
-        <v>296761919.43</v>
+        <v>1125340512.84</v>
       </c>
       <c r="AE2" t="n">
-        <v>-173986115.47</v>
+        <v>-100208943.61</v>
       </c>
       <c r="AF2" t="n">
-        <v>-283331872.6</v>
+        <v>-59797989.03</v>
       </c>
       <c r="AG2" t="n">
-        <v>-1639818.65</v>
+        <v>-565526.6899999999</v>
       </c>
       <c r="AH2" t="n">
-        <v>30244958.22</v>
+        <v>14096332.52</v>
       </c>
       <c r="AI2" t="n">
-        <v>254726733.03</v>
+        <v>46267183.2</v>
       </c>
       <c r="AJ2" t="n">
-        <v>-8564285.98</v>
+        <v>-1000476.2</v>
       </c>
       <c r="AK2" t="n">
-        <v>-167060078.62</v>
+        <v>-101452595.22</v>
       </c>
       <c r="AL2" t="n">
-        <v>239792042.3</v>
+        <v>170949945.78</v>
       </c>
       <c r="AM2" t="n">
-        <v>64167677.7</v>
+        <v>68496874.36</v>
       </c>
       <c r="AN2" t="n">
-        <v>764907957.5599999</v>
+        <v>1285082797.14</v>
       </c>
       <c r="AO2" t="n">
-        <v>440368065.82</v>
+        <v>851387076.89</v>
       </c>
       <c r="AP2" t="n">
-        <v>10835040.92</v>
+        <v>545592770.8200001</v>
       </c>
       <c r="AQ2" t="n">
-        <v>11283828.57</v>
+        <v>7833782.4</v>
       </c>
       <c r="AR2" t="n">
-        <v>11283828.57</v>
+        <v>7833782.4</v>
       </c>
       <c r="AS2" t="n">
-        <v>254526116.05</v>
+        <v>206165740.51</v>
       </c>
       <c r="AT2" t="n">
-        <v>167891937.01</v>
+        <v>173062274.79</v>
       </c>
       <c r="AU2" t="n">
-        <v>86634179.04000001</v>
+        <v>33103465.72</v>
       </c>
       <c r="AV2" t="n">
-        <v>1205276023.38</v>
+        <v>2136469874.03</v>
       </c>
       <c r="AW2" t="n">
-        <v>6490627875.1</v>
+        <v>5420825812.91</v>
       </c>
       <c r="AX2" t="n">
-        <v>7695903898.48</v>
+        <v>7557295686.94</v>
       </c>
       <c r="AY2" t="n">
-        <v>7695903898.48</v>
+        <v>7557295686.94</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>-125774647.209169</v>
+        <v>-12662275.412472</v>
       </c>
       <c r="C3" t="n">
-        <v>0.35692</v>
+        <v>0.248206</v>
       </c>
       <c r="D3" t="n">
-        <v>1190138224.86</v>
+        <v>821886249.97</v>
       </c>
       <c r="E3" t="n">
-        <v>-352389205.78</v>
+        <v>-51015107.68</v>
       </c>
       <c r="F3" t="n">
-        <v>-352389205.78</v>
+        <v>-51015107.68</v>
       </c>
       <c r="G3" t="n">
-        <v>219414836.46</v>
+        <v>334324543.79</v>
       </c>
       <c r="H3" t="n">
-        <v>41978309.49</v>
+        <v>38742646.04</v>
       </c>
       <c r="I3" t="n">
-        <v>6380227569.41</v>
+        <v>2952311621.02</v>
       </c>
       <c r="J3" t="n">
-        <v>837749019.08</v>
+        <v>770871142.29</v>
       </c>
       <c r="K3" t="n">
-        <v>795770709.59</v>
+        <v>732128496.25</v>
       </c>
       <c r="L3" t="n">
-        <v>-3583311.79</v>
+        <v>-2126788.86</v>
       </c>
       <c r="M3" t="n">
-        <v>176743758.66</v>
+        <v>195630734.74</v>
       </c>
       <c r="N3" t="n">
-        <v>124177002.6</v>
+        <v>63357446.79</v>
       </c>
       <c r="O3" t="n">
-        <v>446029395.030831</v>
+        <v>372677376.057528</v>
       </c>
       <c r="P3" t="n">
-        <v>219414836.46</v>
+        <v>334324543.79</v>
       </c>
       <c r="Q3" t="n">
-        <v>6876674372.12</v>
+        <v>3343099193.12</v>
       </c>
       <c r="R3" t="n">
-        <v>602346602.04</v>
+        <v>541916444.9299999</v>
       </c>
       <c r="S3" t="n">
-        <v>812647542</v>
+        <v>796010819</v>
       </c>
       <c r="T3" t="n">
-        <v>812647542</v>
+        <v>796010819</v>
       </c>
       <c r="U3" t="n">
-        <v>0.27</v>
+        <v>0.42</v>
       </c>
       <c r="V3" t="n">
-        <v>0.27</v>
+        <v>0.42</v>
       </c>
       <c r="W3" t="n">
-        <v>219414836.46</v>
+        <v>334324543.79</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>219414836.46</v>
+        <v>334324543.79</v>
       </c>
       <c r="Z3" t="n">
-        <v>-178669205.07</v>
+        <v>-69011048.25</v>
       </c>
       <c r="AA3" t="n">
-        <v>398084041.53</v>
+        <v>403335592.04</v>
       </c>
       <c r="AB3" t="n">
-        <v>398084041.53</v>
+        <v>403335592.04</v>
       </c>
       <c r="AC3" t="n">
-        <v>220942909.4</v>
+        <v>133162169.47</v>
       </c>
       <c r="AD3" t="n">
-        <v>619026950.9299999</v>
+        <v>536497761.51</v>
       </c>
       <c r="AE3" t="n">
-        <v>-35886407.17</v>
+        <v>-137691971.37</v>
       </c>
       <c r="AF3" t="n">
-        <v>-352389205.78</v>
+        <v>-51015107.68</v>
       </c>
       <c r="AG3" t="n">
-        <v>-10251.26</v>
+        <v>-5441483.86</v>
       </c>
       <c r="AH3" t="n">
-        <v>105557131.57</v>
+        <v>47633086.79</v>
       </c>
       <c r="AI3" t="n">
-        <v>246842325.47</v>
+        <v>8823504.75</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-3583311.79</v>
+        <v>-2126788.86</v>
       </c>
       <c r="AK3" t="n">
-        <v>-48983444.27</v>
+        <v>-130146499.09</v>
       </c>
       <c r="AL3" t="n">
-        <v>176743758.66</v>
+        <v>195630734.74</v>
       </c>
       <c r="AM3" t="n">
-        <v>124177002.6</v>
+        <v>63357446.79</v>
       </c>
       <c r="AN3" t="n">
-        <v>1020744616.29</v>
+        <v>682785626.12</v>
       </c>
       <c r="AO3" t="n">
-        <v>496446802.71</v>
+        <v>390787572.1</v>
       </c>
       <c r="AP3" t="n">
-        <v>37300450.59</v>
+        <v>173863659.12</v>
       </c>
       <c r="AQ3" t="n">
-        <v>11339671.77</v>
+        <v>10447076.09</v>
       </c>
       <c r="AR3" t="n">
-        <v>11339671.77</v>
+        <v>10447076.09</v>
       </c>
       <c r="AS3" t="n">
-        <v>318502931.59</v>
+        <v>128003693.68</v>
       </c>
       <c r="AT3" t="n">
-        <v>168511857.63</v>
+        <v>80905526.09</v>
       </c>
       <c r="AU3" t="n">
-        <v>149991073.96</v>
+        <v>47098167.59</v>
       </c>
       <c r="AV3" t="n">
-        <v>1517191419</v>
+        <v>1073573198.22</v>
       </c>
       <c r="AW3" t="n">
-        <v>6380227569.41</v>
+        <v>2952311621.02</v>
       </c>
       <c r="AX3" t="n">
-        <v>7897418988.41</v>
+        <v>4025884819.24</v>
       </c>
       <c r="AY3" t="n">
-        <v>7897418988.41</v>
+        <v>4025884819.24</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>-12662275.412472</v>
+        <v>-125774647.209169</v>
       </c>
       <c r="C4" t="n">
-        <v>0.248206</v>
+        <v>0.35692</v>
       </c>
       <c r="D4" t="n">
-        <v>821886249.97</v>
+        <v>1190138224.86</v>
       </c>
       <c r="E4" t="n">
-        <v>-51015107.68</v>
+        <v>-352389205.78</v>
       </c>
       <c r="F4" t="n">
-        <v>-51015107.68</v>
+        <v>-352389205.78</v>
       </c>
       <c r="G4" t="n">
-        <v>334324543.79</v>
+        <v>219414836.46</v>
       </c>
       <c r="H4" t="n">
-        <v>38742646.04</v>
+        <v>41978309.49</v>
       </c>
       <c r="I4" t="n">
-        <v>2952311621.02</v>
+        <v>6380227569.41</v>
       </c>
       <c r="J4" t="n">
-        <v>770871142.29</v>
+        <v>837749019.08</v>
       </c>
       <c r="K4" t="n">
-        <v>732128496.25</v>
+        <v>795770709.59</v>
       </c>
       <c r="L4" t="n">
-        <v>-2126788.86</v>
+        <v>-3583311.79</v>
       </c>
       <c r="M4" t="n">
-        <v>195630734.74</v>
+        <v>176743758.66</v>
       </c>
       <c r="N4" t="n">
-        <v>63357446.79</v>
+        <v>124177002.6</v>
       </c>
       <c r="O4" t="n">
-        <v>372677376.057528</v>
+        <v>446029395.030831</v>
       </c>
       <c r="P4" t="n">
-        <v>334324543.79</v>
+        <v>219414836.46</v>
       </c>
       <c r="Q4" t="n">
-        <v>3343099193.12</v>
+        <v>6876674372.12</v>
       </c>
       <c r="R4" t="n">
-        <v>541916444.9299999</v>
+        <v>602346602.04</v>
       </c>
       <c r="S4" t="n">
-        <v>796010819</v>
+        <v>812647542</v>
       </c>
       <c r="T4" t="n">
-        <v>796010819</v>
+        <v>812647542</v>
       </c>
       <c r="U4" t="n">
-        <v>0.42</v>
+        <v>0.27</v>
       </c>
       <c r="V4" t="n">
-        <v>0.42</v>
+        <v>0.27</v>
       </c>
       <c r="W4" t="n">
-        <v>334324543.79</v>
+        <v>219414836.46</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>334324543.79</v>
+        <v>219414836.46</v>
       </c>
       <c r="Z4" t="n">
-        <v>-69011048.25</v>
+        <v>-178669205.07</v>
       </c>
       <c r="AA4" t="n">
-        <v>403335592.04</v>
+        <v>398084041.53</v>
       </c>
       <c r="AB4" t="n">
-        <v>403335592.04</v>
+        <v>398084041.53</v>
       </c>
       <c r="AC4" t="n">
-        <v>133162169.47</v>
+        <v>220942909.4</v>
       </c>
       <c r="AD4" t="n">
-        <v>536497761.51</v>
+        <v>619026950.9299999</v>
       </c>
       <c r="AE4" t="n">
-        <v>-137691971.37</v>
+        <v>-35886407.17</v>
       </c>
       <c r="AF4" t="n">
-        <v>-51015107.68</v>
+        <v>-352389205.78</v>
       </c>
       <c r="AG4" t="n">
-        <v>-5441483.86</v>
+        <v>-10251.26</v>
       </c>
       <c r="AH4" t="n">
-        <v>47633086.79</v>
+        <v>105557131.57</v>
       </c>
       <c r="AI4" t="n">
-        <v>8823504.75</v>
+        <v>246842325.47</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-2126788.86</v>
+        <v>-3583311.79</v>
       </c>
       <c r="AK4" t="n">
-        <v>-130146499.09</v>
+        <v>-48983444.27</v>
       </c>
       <c r="AL4" t="n">
-        <v>195630734.74</v>
+        <v>176743758.66</v>
       </c>
       <c r="AM4" t="n">
-        <v>63357446.79</v>
+        <v>124177002.6</v>
       </c>
       <c r="AN4" t="n">
-        <v>682785626.12</v>
+        <v>1020744616.29</v>
       </c>
       <c r="AO4" t="n">
-        <v>390787572.1</v>
+        <v>496446802.71</v>
       </c>
       <c r="AP4" t="n">
-        <v>173863659.12</v>
+        <v>37300450.59</v>
       </c>
       <c r="AQ4" t="n">
-        <v>10447076.09</v>
+        <v>11339671.77</v>
       </c>
       <c r="AR4" t="n">
-        <v>10447076.09</v>
+        <v>11339671.77</v>
       </c>
       <c r="AS4" t="n">
-        <v>128003693.68</v>
+        <v>318502931.59</v>
       </c>
       <c r="AT4" t="n">
-        <v>80905526.09</v>
+        <v>168511857.63</v>
       </c>
       <c r="AU4" t="n">
-        <v>47098167.59</v>
+        <v>149991073.96</v>
       </c>
       <c r="AV4" t="n">
-        <v>1073573198.22</v>
+        <v>1517191419</v>
       </c>
       <c r="AW4" t="n">
-        <v>2952311621.02</v>
+        <v>6380227569.41</v>
       </c>
       <c r="AX4" t="n">
-        <v>4025884819.24</v>
+        <v>7897418988.41</v>
       </c>
       <c r="AY4" t="n">
-        <v>4025884819.24</v>
+        <v>7897418988.41</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>-11962454.652747</v>
+        <v>-68919534.8175</v>
       </c>
       <c r="C5" t="n">
-        <v>0.200048</v>
+        <v>0.25</v>
       </c>
       <c r="D5" t="n">
-        <v>1394202701.3</v>
+        <v>890149421.4</v>
       </c>
       <c r="E5" t="n">
-        <v>-59797989.03</v>
+        <v>-275678139.27</v>
       </c>
       <c r="F5" t="n">
-        <v>-59797989.03</v>
+        <v>-275678139.27</v>
       </c>
       <c r="G5" t="n">
-        <v>876920607.1799999</v>
+        <v>-56572549.96</v>
       </c>
       <c r="H5" t="n">
-        <v>38114253.65</v>
+        <v>77917320.40000001</v>
       </c>
       <c r="I5" t="n">
-        <v>5420825812.91</v>
+        <v>6490627875.1</v>
       </c>
       <c r="J5" t="n">
-        <v>1334404712.27</v>
+        <v>614471282.13</v>
       </c>
       <c r="K5" t="n">
-        <v>1296290458.62</v>
+        <v>536553961.73</v>
       </c>
       <c r="L5" t="n">
-        <v>-1000476.2</v>
+        <v>-8564285.98</v>
       </c>
       <c r="M5" t="n">
-        <v>170949945.78</v>
+        <v>239792042.3</v>
       </c>
       <c r="N5" t="n">
-        <v>68496874.36</v>
+        <v>64167677.7</v>
       </c>
       <c r="O5" t="n">
-        <v>924756141.557253</v>
+        <v>150186054.4925</v>
       </c>
       <c r="P5" t="n">
-        <v>876920607.1799999</v>
+        <v>-56572549.96</v>
       </c>
       <c r="Q5" t="n">
-        <v>6272212889.8</v>
+        <v>6930995940.92</v>
       </c>
       <c r="R5" t="n">
-        <v>1123096385.03</v>
+        <v>295123670.3</v>
       </c>
       <c r="S5" t="n">
-        <v>804514319</v>
+        <v>808179285</v>
       </c>
       <c r="T5" t="n">
-        <v>804514319</v>
+        <v>808179285</v>
       </c>
       <c r="U5" t="n">
-        <v>1.09</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="V5" t="n">
-        <v>1.09</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="W5" t="n">
-        <v>876920607.1799999</v>
+        <v>-56572549.96</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>876920607.1799999</v>
+        <v>-56572549.96</v>
       </c>
       <c r="Z5" t="n">
-        <v>-23298039.99</v>
+        <v>-152246600.38</v>
       </c>
       <c r="AA5" t="n">
-        <v>900218647.17</v>
+        <v>95674050.42</v>
       </c>
       <c r="AB5" t="n">
-        <v>900218647.17</v>
+        <v>95674050.42</v>
       </c>
       <c r="AC5" t="n">
-        <v>225121865.67</v>
+        <v>201087869.01</v>
       </c>
       <c r="AD5" t="n">
-        <v>1125340512.84</v>
+        <v>296761919.43</v>
       </c>
       <c r="AE5" t="n">
-        <v>-100208943.61</v>
+        <v>-173986115.47</v>
       </c>
       <c r="AF5" t="n">
-        <v>-59797989.03</v>
+        <v>-283331872.6</v>
       </c>
       <c r="AG5" t="n">
-        <v>-565526.6899999999</v>
+        <v>-1639818.65</v>
       </c>
       <c r="AH5" t="n">
-        <v>14096332.52</v>
+        <v>30244958.22</v>
       </c>
       <c r="AI5" t="n">
-        <v>46267183.2</v>
+        <v>254726733.03</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-1000476.2</v>
+        <v>-8564285.98</v>
       </c>
       <c r="AK5" t="n">
-        <v>-101452595.22</v>
+        <v>-167060078.62</v>
       </c>
       <c r="AL5" t="n">
-        <v>170949945.78</v>
+        <v>239792042.3</v>
       </c>
       <c r="AM5" t="n">
-        <v>68496874.36</v>
+        <v>64167677.7</v>
       </c>
       <c r="AN5" t="n">
-        <v>1285082797.14</v>
+        <v>764907957.5599999</v>
       </c>
       <c r="AO5" t="n">
-        <v>851387076.89</v>
+        <v>440368065.82</v>
       </c>
       <c r="AP5" t="n">
-        <v>545592770.8200001</v>
+        <v>10835040.92</v>
       </c>
       <c r="AQ5" t="n">
-        <v>7833782.4</v>
+        <v>11283828.57</v>
       </c>
       <c r="AR5" t="n">
-        <v>7833782.4</v>
+        <v>11283828.57</v>
       </c>
       <c r="AS5" t="n">
-        <v>206165740.51</v>
+        <v>254526116.05</v>
       </c>
       <c r="AT5" t="n">
-        <v>173062274.79</v>
+        <v>167891937.01</v>
       </c>
       <c r="AU5" t="n">
-        <v>33103465.72</v>
+        <v>86634179.04000001</v>
       </c>
       <c r="AV5" t="n">
-        <v>2136469874.03</v>
+        <v>1205276023.38</v>
       </c>
       <c r="AW5" t="n">
-        <v>5420825812.91</v>
+        <v>6490627875.1</v>
       </c>
       <c r="AX5" t="n">
-        <v>7557295686.94</v>
+        <v>7695903898.48</v>
       </c>
       <c r="AY5" t="n">
-        <v>7557295686.94</v>
+        <v>7695903898.48</v>
       </c>
     </row>
   </sheetData>
@@ -1648,83 +1648,197 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46022</v>
-      </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
+        <v>44561</v>
+      </c>
+      <c r="B2" t="n">
+        <v>803291894</v>
+      </c>
+      <c r="C2" t="n">
+        <v>803291894</v>
+      </c>
       <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr"/>
-      <c r="X2" t="inlineStr"/>
-      <c r="Y2" t="inlineStr"/>
-      <c r="Z2" t="inlineStr"/>
-      <c r="AA2" t="inlineStr"/>
-      <c r="AB2" t="inlineStr"/>
-      <c r="AC2" t="inlineStr"/>
-      <c r="AD2" t="inlineStr"/>
-      <c r="AE2" t="inlineStr"/>
+      <c r="E2" t="n">
+        <v>3466648861.53</v>
+      </c>
+      <c r="F2" t="n">
+        <v>6156923014.26</v>
+      </c>
+      <c r="G2" t="n">
+        <v>8846078962.969999</v>
+      </c>
+      <c r="H2" t="n">
+        <v>8196371696.89</v>
+      </c>
+      <c r="I2" t="n">
+        <v>6156923014.26</v>
+      </c>
+      <c r="J2" t="n">
+        <v>6159715502.58</v>
+      </c>
+      <c r="K2" t="n">
+        <v>8695848268.530001</v>
+      </c>
+      <c r="L2" t="n">
+        <v>7110056912.3</v>
+      </c>
+      <c r="M2" t="n">
+        <v>950341409.72</v>
+      </c>
+      <c r="N2" t="n">
+        <v>6159715502.58</v>
+      </c>
+      <c r="O2" t="n">
+        <v>3132559861.18</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1792491348.68</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>803291894</v>
+      </c>
+      <c r="R2" t="n">
+        <v>803291894</v>
+      </c>
+      <c r="S2" t="n">
+        <v>15447274379.3</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2643298266.11</v>
+      </c>
+      <c r="U2" t="n">
+        <v>76969956.45</v>
+      </c>
+      <c r="V2" t="n">
+        <v>16320928.32</v>
+      </c>
+      <c r="W2" t="n">
+        <v>13874615.39</v>
+      </c>
+      <c r="X2" t="n">
+        <v>2536132765.95</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>2536132765.95</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>12803976113.19</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>515765590.44</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>930516095.58</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>150230694.44</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>5699152824.02</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>3461777577.79</v>
+      </c>
       <c r="AF2" t="inlineStr"/>
-      <c r="AG2" t="inlineStr"/>
-      <c r="AH2" t="inlineStr"/>
-      <c r="AI2" t="inlineStr"/>
-      <c r="AJ2" t="inlineStr"/>
+      <c r="AG2" t="n">
+        <v>1203055466.79</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>1034319779.44</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>22557331291.6</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>1556983481.52</v>
+      </c>
       <c r="AK2" t="inlineStr"/>
-      <c r="AL2" t="inlineStr"/>
-      <c r="AM2" t="inlineStr"/>
+      <c r="AL2" t="n">
+        <v>3603309.71</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>38479828.35</v>
+      </c>
       <c r="AN2" t="inlineStr"/>
       <c r="AO2" t="inlineStr"/>
-      <c r="AP2" t="inlineStr"/>
-      <c r="AQ2" t="inlineStr"/>
-      <c r="AR2" t="inlineStr"/>
-      <c r="AS2" t="inlineStr"/>
-      <c r="AT2" t="inlineStr"/>
-      <c r="AU2" t="inlineStr"/>
-      <c r="AV2" t="inlineStr"/>
-      <c r="AW2" t="inlineStr"/>
-      <c r="AX2" t="inlineStr"/>
-      <c r="AY2" t="inlineStr"/>
-      <c r="AZ2" t="inlineStr"/>
-      <c r="BA2" t="inlineStr"/>
-      <c r="BB2" t="inlineStr"/>
-      <c r="BC2" t="inlineStr"/>
-      <c r="BD2" t="inlineStr"/>
-      <c r="BE2" t="inlineStr"/>
-      <c r="BF2" t="inlineStr"/>
-      <c r="BG2" t="inlineStr"/>
-      <c r="BH2" t="inlineStr"/>
-      <c r="BI2" t="inlineStr"/>
-      <c r="BJ2" t="n">
-        <v>-60834827.57</v>
-      </c>
-      <c r="BK2" t="n">
-        <v>589423402.1799999</v>
-      </c>
-      <c r="BL2" t="inlineStr"/>
+      <c r="AP2" t="n">
+        <v>408865678.98</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>971512572.74</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>2792488.32</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>2631475.64</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>161012.68</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>114120380.41</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>-39759986.47</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>153880366.88</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>6460656.87</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>19222432.36</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>15002523.77</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>113194753.88</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>21000347810.08</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>882131562.9299999</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>1659441.87</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>16233733996.06</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>16233733996.06</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>259578104.3</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>52544359.45</v>
+      </c>
+      <c r="BJ2" t="inlineStr"/>
+      <c r="BK2" t="inlineStr"/>
+      <c r="BL2" t="n">
+        <v>3570700345.47</v>
+      </c>
       <c r="BM2" t="inlineStr"/>
-      <c r="BN2" t="inlineStr"/>
-      <c r="BO2" t="inlineStr"/>
-      <c r="BP2" t="inlineStr"/>
+      <c r="BN2" t="n">
+        <v>3570700345.47</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>705984881.27</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>2864715464.2</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45657</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
         <v>803291894</v>
@@ -1733,40 +1847,40 @@
         <v>803291894</v>
       </c>
       <c r="D3" t="n">
-        <v>3316017257.73</v>
+        <v>3332572634.53</v>
       </c>
       <c r="E3" t="n">
-        <v>10240730134.89</v>
+        <v>9473302407.09</v>
       </c>
       <c r="F3" t="n">
-        <v>6456965868.63</v>
+        <v>6411431407.54</v>
       </c>
       <c r="G3" t="n">
-        <v>15149067744.66</v>
+        <v>14447561419.57</v>
       </c>
       <c r="H3" t="n">
-        <v>13287013998.3</v>
+        <v>15254399489.77</v>
       </c>
       <c r="I3" t="n">
-        <v>6456965868.63</v>
+        <v>6411431407.54</v>
       </c>
       <c r="J3" t="n">
-        <v>6468108737.78</v>
+        <v>6413710856.97</v>
       </c>
       <c r="K3" t="n">
-        <v>13766305423.87</v>
+        <v>13796557669.59</v>
       </c>
       <c r="L3" t="n">
-        <v>9752887321.690001</v>
+        <v>9406232514.940001</v>
       </c>
       <c r="M3" t="n">
-        <v>3284778583.91</v>
+        <v>2992521657.97</v>
       </c>
       <c r="N3" t="n">
-        <v>6468108737.78</v>
+        <v>6413710856.97</v>
       </c>
       <c r="O3" t="n">
-        <v>3338214133.23</v>
+        <v>3283816252.42</v>
       </c>
       <c r="P3" t="n">
         <v>1792491348.68</v>
@@ -1778,148 +1892,146 @@
         <v>803291894</v>
       </c>
       <c r="S3" t="n">
-        <v>28972680647.36</v>
+        <v>24042684260.71</v>
       </c>
       <c r="T3" t="n">
-        <v>7328030300.63</v>
+        <v>7410995298.47</v>
       </c>
       <c r="U3" t="n">
-        <v>702513.47</v>
+        <v>717455.24</v>
       </c>
       <c r="V3" t="n">
-        <v>27822642.07</v>
+        <v>25286798.03</v>
       </c>
       <c r="W3" t="n">
-        <v>1308459</v>
+        <v>2144232.58</v>
       </c>
       <c r="X3" t="n">
-        <v>7298196686.09</v>
+        <v>7382846812.62</v>
       </c>
       <c r="Y3" t="n">
-        <v>7298196686.09</v>
+        <v>7382846812.62</v>
       </c>
       <c r="Z3" t="n">
-        <v>21644650346.73</v>
+        <v>16631688962.24</v>
       </c>
       <c r="AA3" t="n">
-        <v>1118207732.78</v>
+        <v>866994563.13</v>
       </c>
       <c r="AB3" t="n">
-        <v>2942533448.8</v>
+        <v>2090455594.47</v>
       </c>
       <c r="AC3" t="n">
-        <v>1382762320.79</v>
+        <v>651003749.98</v>
       </c>
       <c r="AD3" t="n">
-        <v>5389868874.38</v>
+        <v>4165622178.7</v>
       </c>
       <c r="AE3" t="n">
-        <v>2723199092.24</v>
+        <v>1875136176.15</v>
       </c>
       <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="n">
-        <v>224564008.18</v>
+        <v>624472856.36</v>
       </c>
       <c r="AH3" t="n">
-        <v>2442105773.96</v>
+        <v>1666013146.19</v>
       </c>
       <c r="AI3" t="n">
-        <v>38725567969.05</v>
+        <v>33448916775.65</v>
       </c>
       <c r="AJ3" t="n">
-        <v>3793903624.02</v>
-      </c>
-      <c r="AK3" t="inlineStr"/>
+        <v>1562828323.64</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>2282358.49</v>
+      </c>
       <c r="AL3" t="n">
-        <v>12016342.9</v>
+        <v>10325743.02</v>
       </c>
       <c r="AM3" t="n">
-        <v>150872358.94</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>290399988.42</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>290399988.42</v>
-      </c>
+        <v>68777547.8</v>
+      </c>
+      <c r="AN3" t="inlineStr"/>
+      <c r="AO3" t="inlineStr"/>
       <c r="AP3" t="n">
-        <v>608471924.66</v>
+        <v>453439853.61</v>
       </c>
       <c r="AQ3" t="n">
-        <v>2474230028.22</v>
+        <v>888121622.05</v>
       </c>
       <c r="AR3" t="n">
-        <v>11142869.15</v>
+        <v>2279449.43</v>
       </c>
       <c r="AS3" t="n">
-        <v>11015443.46</v>
+        <v>2146608.08</v>
       </c>
       <c r="AT3" t="n">
-        <v>127425.69</v>
+        <v>132841.35</v>
       </c>
       <c r="AU3" t="n">
-        <v>147007472.03</v>
+        <v>128500659.44</v>
       </c>
       <c r="AV3" t="n">
-        <v>-55483793.08</v>
+        <v>-44795367.68</v>
       </c>
       <c r="AW3" t="n">
-        <v>202491265.11</v>
+        <v>173296027.12</v>
       </c>
       <c r="AX3" t="n">
-        <v>106100.02</v>
+        <v>5444848.48</v>
       </c>
       <c r="AY3" t="n">
-        <v>24297436.04</v>
+        <v>23201148.64</v>
       </c>
       <c r="AZ3" t="n">
-        <v>12040180.63</v>
+        <v>14523468.16</v>
       </c>
       <c r="BA3" t="n">
-        <v>166047548.42</v>
+        <v>130126561.84</v>
       </c>
       <c r="BB3" t="n">
-        <v>34931664345.03</v>
+        <v>31886088452.01</v>
       </c>
       <c r="BC3" t="n">
-        <v>1801873052.03</v>
+        <v>1720710211.61</v>
       </c>
       <c r="BD3" t="n">
-        <v>1642296835.28</v>
+        <v>1447170.17</v>
       </c>
       <c r="BE3" t="n">
-        <v>22892791011.44</v>
+        <v>23068664909.56</v>
       </c>
       <c r="BF3" t="n">
         <v>0</v>
       </c>
       <c r="BG3" t="n">
-        <v>22892791011.44</v>
+        <v>23068664909.56</v>
       </c>
       <c r="BH3" t="n">
-        <v>2890735853.79</v>
+        <v>2117613882.04</v>
       </c>
       <c r="BI3" t="n">
-        <v>339025843.34</v>
+        <v>276374350.56</v>
       </c>
       <c r="BJ3" t="n">
-        <v>-34332285.35</v>
+        <v>-25138028.75</v>
       </c>
       <c r="BK3" t="n">
-        <v>373358128.69</v>
+        <v>301512379.31</v>
       </c>
       <c r="BL3" t="n">
-        <v>5364941749.15</v>
+        <v>4701277928.07</v>
       </c>
       <c r="BM3" t="inlineStr"/>
       <c r="BN3" t="n">
-        <v>5364941749.15</v>
+        <v>4701277928.07</v>
       </c>
       <c r="BO3" t="n">
-        <v>124462031.41</v>
+        <v>119444900.61</v>
       </c>
       <c r="BP3" t="n">
-        <v>5240479717.74</v>
+        <v>4581833027.46</v>
       </c>
     </row>
     <row r="4">
@@ -2124,7 +2236,7 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44926</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
         <v>803291894</v>
@@ -2133,40 +2245,40 @@
         <v>803291894</v>
       </c>
       <c r="D5" t="n">
-        <v>3332572634.53</v>
+        <v>3316017257.73</v>
       </c>
       <c r="E5" t="n">
-        <v>9473302407.09</v>
+        <v>10240730134.89</v>
       </c>
       <c r="F5" t="n">
-        <v>6411431407.54</v>
+        <v>6456965868.63</v>
       </c>
       <c r="G5" t="n">
-        <v>14447561419.57</v>
+        <v>15149067744.66</v>
       </c>
       <c r="H5" t="n">
-        <v>15254399489.77</v>
+        <v>13287013998.3</v>
       </c>
       <c r="I5" t="n">
-        <v>6411431407.54</v>
+        <v>6456965868.63</v>
       </c>
       <c r="J5" t="n">
-        <v>6413710856.97</v>
+        <v>6468108737.78</v>
       </c>
       <c r="K5" t="n">
-        <v>13796557669.59</v>
+        <v>13766305423.87</v>
       </c>
       <c r="L5" t="n">
-        <v>9406232514.940001</v>
+        <v>9752887321.690001</v>
       </c>
       <c r="M5" t="n">
-        <v>2992521657.97</v>
+        <v>3284778583.91</v>
       </c>
       <c r="N5" t="n">
-        <v>6413710856.97</v>
+        <v>6468108737.78</v>
       </c>
       <c r="O5" t="n">
-        <v>3283816252.42</v>
+        <v>3338214133.23</v>
       </c>
       <c r="P5" t="n">
         <v>1792491348.68</v>
@@ -2178,337 +2290,225 @@
         <v>803291894</v>
       </c>
       <c r="S5" t="n">
-        <v>24042684260.71</v>
+        <v>28972680647.36</v>
       </c>
       <c r="T5" t="n">
-        <v>7410995298.47</v>
+        <v>7328030300.63</v>
       </c>
       <c r="U5" t="n">
-        <v>717455.24</v>
+        <v>702513.47</v>
       </c>
       <c r="V5" t="n">
-        <v>25286798.03</v>
+        <v>27822642.07</v>
       </c>
       <c r="W5" t="n">
-        <v>2144232.58</v>
+        <v>1308459</v>
       </c>
       <c r="X5" t="n">
-        <v>7382846812.62</v>
+        <v>7298196686.09</v>
       </c>
       <c r="Y5" t="n">
-        <v>7382846812.62</v>
+        <v>7298196686.09</v>
       </c>
       <c r="Z5" t="n">
-        <v>16631688962.24</v>
+        <v>21644650346.73</v>
       </c>
       <c r="AA5" t="n">
-        <v>866994563.13</v>
+        <v>1118207732.78</v>
       </c>
       <c r="AB5" t="n">
-        <v>2090455594.47</v>
+        <v>2942533448.8</v>
       </c>
       <c r="AC5" t="n">
-        <v>651003749.98</v>
+        <v>1382762320.79</v>
       </c>
       <c r="AD5" t="n">
-        <v>4165622178.7</v>
+        <v>5389868874.38</v>
       </c>
       <c r="AE5" t="n">
-        <v>1875136176.15</v>
+        <v>2723199092.24</v>
       </c>
       <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="n">
-        <v>624472856.36</v>
+        <v>224564008.18</v>
       </c>
       <c r="AH5" t="n">
-        <v>1666013146.19</v>
+        <v>2442105773.96</v>
       </c>
       <c r="AI5" t="n">
-        <v>33448916775.65</v>
+        <v>38725567969.05</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1562828323.64</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>2282358.49</v>
-      </c>
+        <v>3793903624.02</v>
+      </c>
+      <c r="AK5" t="inlineStr"/>
       <c r="AL5" t="n">
-        <v>10325743.02</v>
+        <v>12016342.9</v>
       </c>
       <c r="AM5" t="n">
-        <v>68777547.8</v>
-      </c>
-      <c r="AN5" t="inlineStr"/>
-      <c r="AO5" t="inlineStr"/>
+        <v>150872358.94</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>290399988.42</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>290399988.42</v>
+      </c>
       <c r="AP5" t="n">
-        <v>453439853.61</v>
+        <v>608471924.66</v>
       </c>
       <c r="AQ5" t="n">
-        <v>888121622.05</v>
+        <v>2474230028.22</v>
       </c>
       <c r="AR5" t="n">
-        <v>2279449.43</v>
+        <v>11142869.15</v>
       </c>
       <c r="AS5" t="n">
-        <v>2146608.08</v>
+        <v>11015443.46</v>
       </c>
       <c r="AT5" t="n">
-        <v>132841.35</v>
+        <v>127425.69</v>
       </c>
       <c r="AU5" t="n">
-        <v>128500659.44</v>
+        <v>147007472.03</v>
       </c>
       <c r="AV5" t="n">
-        <v>-44795367.68</v>
+        <v>-55483793.08</v>
       </c>
       <c r="AW5" t="n">
-        <v>173296027.12</v>
+        <v>202491265.11</v>
       </c>
       <c r="AX5" t="n">
-        <v>5444848.48</v>
+        <v>106100.02</v>
       </c>
       <c r="AY5" t="n">
-        <v>23201148.64</v>
+        <v>24297436.04</v>
       </c>
       <c r="AZ5" t="n">
-        <v>14523468.16</v>
+        <v>12040180.63</v>
       </c>
       <c r="BA5" t="n">
-        <v>130126561.84</v>
+        <v>166047548.42</v>
       </c>
       <c r="BB5" t="n">
-        <v>31886088452.01</v>
+        <v>34931664345.03</v>
       </c>
       <c r="BC5" t="n">
-        <v>1720710211.61</v>
+        <v>1801873052.03</v>
       </c>
       <c r="BD5" t="n">
-        <v>1447170.17</v>
+        <v>1642296835.28</v>
       </c>
       <c r="BE5" t="n">
-        <v>23068664909.56</v>
+        <v>22892791011.44</v>
       </c>
       <c r="BF5" t="n">
         <v>0</v>
       </c>
       <c r="BG5" t="n">
-        <v>23068664909.56</v>
+        <v>22892791011.44</v>
       </c>
       <c r="BH5" t="n">
-        <v>2117613882.04</v>
+        <v>2890735853.79</v>
       </c>
       <c r="BI5" t="n">
-        <v>276374350.56</v>
+        <v>339025843.34</v>
       </c>
       <c r="BJ5" t="n">
-        <v>-25138028.75</v>
+        <v>-34332285.35</v>
       </c>
       <c r="BK5" t="n">
-        <v>301512379.31</v>
+        <v>373358128.69</v>
       </c>
       <c r="BL5" t="n">
-        <v>4701277928.07</v>
+        <v>5364941749.15</v>
       </c>
       <c r="BM5" t="inlineStr"/>
       <c r="BN5" t="n">
-        <v>4701277928.07</v>
+        <v>5364941749.15</v>
       </c>
       <c r="BO5" t="n">
-        <v>119444900.61</v>
+        <v>124462031.41</v>
       </c>
       <c r="BP5" t="n">
-        <v>4581833027.46</v>
+        <v>5240479717.74</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>44561</v>
-      </c>
-      <c r="B6" t="n">
-        <v>803291894</v>
-      </c>
-      <c r="C6" t="n">
-        <v>803291894</v>
-      </c>
+        <v>46022</v>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
-      <c r="E6" t="n">
-        <v>3466648861.53</v>
-      </c>
-      <c r="F6" t="n">
-        <v>6156923014.26</v>
-      </c>
-      <c r="G6" t="n">
-        <v>8846078962.969999</v>
-      </c>
-      <c r="H6" t="n">
-        <v>8196371696.89</v>
-      </c>
-      <c r="I6" t="n">
-        <v>6156923014.26</v>
-      </c>
-      <c r="J6" t="n">
-        <v>6159715502.58</v>
-      </c>
-      <c r="K6" t="n">
-        <v>8695848268.530001</v>
-      </c>
-      <c r="L6" t="n">
-        <v>7110056912.3</v>
-      </c>
-      <c r="M6" t="n">
-        <v>950341409.72</v>
-      </c>
-      <c r="N6" t="n">
-        <v>6159715502.58</v>
-      </c>
-      <c r="O6" t="n">
-        <v>3132559861.18</v>
-      </c>
-      <c r="P6" t="n">
-        <v>1792491348.68</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>803291894</v>
-      </c>
-      <c r="R6" t="n">
-        <v>803291894</v>
-      </c>
-      <c r="S6" t="n">
-        <v>15447274379.3</v>
-      </c>
-      <c r="T6" t="n">
-        <v>2643298266.11</v>
-      </c>
-      <c r="U6" t="n">
-        <v>76969956.45</v>
-      </c>
-      <c r="V6" t="n">
-        <v>16320928.32</v>
-      </c>
-      <c r="W6" t="n">
-        <v>13874615.39</v>
-      </c>
-      <c r="X6" t="n">
-        <v>2536132765.95</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>2536132765.95</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>12803976113.19</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>515765590.44</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>930516095.58</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>150230694.44</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>5699152824.02</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>3461777577.79</v>
-      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
-      <c r="AG6" t="n">
-        <v>1203055466.79</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>1034319779.44</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>22557331291.6</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>1556983481.52</v>
-      </c>
+      <c r="AG6" t="inlineStr"/>
+      <c r="AH6" t="inlineStr"/>
+      <c r="AI6" t="inlineStr"/>
+      <c r="AJ6" t="inlineStr"/>
       <c r="AK6" t="inlineStr"/>
-      <c r="AL6" t="n">
-        <v>3603309.71</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>38479828.35</v>
-      </c>
+      <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="inlineStr"/>
       <c r="AN6" t="inlineStr"/>
       <c r="AO6" t="inlineStr"/>
-      <c r="AP6" t="n">
-        <v>408865678.98</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>971512572.74</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>2792488.32</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>2631475.64</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>161012.68</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>114120380.41</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>-39759986.47</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>153880366.88</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>6460656.87</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>19222432.36</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>15002523.77</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>113194753.88</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>21000347810.08</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>882131562.9299999</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>1659441.87</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>16233733996.06</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>16233733996.06</v>
-      </c>
-      <c r="BH6" t="n">
-        <v>259578104.3</v>
-      </c>
-      <c r="BI6" t="n">
-        <v>52544359.45</v>
-      </c>
-      <c r="BJ6" t="inlineStr"/>
-      <c r="BK6" t="inlineStr"/>
-      <c r="BL6" t="n">
-        <v>3570700345.47</v>
-      </c>
+      <c r="AP6" t="inlineStr"/>
+      <c r="AQ6" t="inlineStr"/>
+      <c r="AR6" t="inlineStr"/>
+      <c r="AS6" t="inlineStr"/>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AU6" t="inlineStr"/>
+      <c r="AV6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr"/>
+      <c r="AX6" t="inlineStr"/>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr"/>
+      <c r="BA6" t="inlineStr"/>
+      <c r="BB6" t="inlineStr"/>
+      <c r="BC6" t="inlineStr"/>
+      <c r="BD6" t="inlineStr"/>
+      <c r="BE6" t="inlineStr"/>
+      <c r="BF6" t="inlineStr"/>
+      <c r="BG6" t="inlineStr"/>
+      <c r="BH6" t="inlineStr"/>
+      <c r="BI6" t="inlineStr"/>
+      <c r="BJ6" t="n">
+        <v>-60834827.57</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>589423402.1799999</v>
+      </c>
+      <c r="BL6" t="inlineStr"/>
       <c r="BM6" t="inlineStr"/>
-      <c r="BN6" t="n">
-        <v>3570700345.47</v>
-      </c>
-      <c r="BO6" t="n">
-        <v>705984881.27</v>
-      </c>
-      <c r="BP6" t="n">
-        <v>2864715464.2</v>
-      </c>
+      <c r="BN6" t="inlineStr"/>
+      <c r="BO6" t="inlineStr"/>
+      <c r="BP6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2758,562 +2758,562 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>-142133434.55</v>
+        <v>-2619399794.22</v>
       </c>
       <c r="C2" t="n">
-        <v>-4042921513.07</v>
+        <v>-2002233824.68</v>
       </c>
       <c r="D2" t="n">
-        <v>5335007912.6</v>
+        <v>1989626375.5</v>
       </c>
       <c r="E2" t="n">
-        <v>-4408840.55</v>
+        <v>-14056278.77</v>
       </c>
       <c r="F2" t="n">
-        <v>5240479717.74</v>
+        <v>2864715464.2</v>
       </c>
       <c r="G2" t="n">
-        <v>3745741027.91</v>
+        <v>3170244377.7</v>
       </c>
       <c r="H2" t="n">
-        <v>1494738689.83</v>
+        <v>-305528913.5</v>
       </c>
       <c r="I2" t="n">
-        <v>2153660056.15</v>
+        <v>2476093066.69</v>
       </c>
       <c r="J2" t="n">
-        <v>1343693831.47</v>
+        <v>2828542708.5</v>
       </c>
       <c r="K2" t="n">
-        <v>-398120174.85</v>
+        <v>-339842192.63</v>
       </c>
       <c r="L2" t="n">
-        <v>1292086399.53</v>
+        <v>-12607449.18</v>
       </c>
       <c r="M2" t="n">
-        <v>1292086399.53</v>
+        <v>-12607449.18</v>
       </c>
       <c r="N2" t="n">
-        <v>-4042921513.07</v>
+        <v>-2002233824.68</v>
       </c>
       <c r="O2" t="n">
-        <v>5335007912.6</v>
+        <v>1989626375.5</v>
       </c>
       <c r="P2" t="n">
-        <v>-521196772.32</v>
+        <v>-176278464.74</v>
       </c>
       <c r="Q2" t="n">
-        <v>-395768641.08</v>
+        <v>-107263233.97</v>
       </c>
       <c r="R2" t="n">
-        <v>-123620183.25</v>
-      </c>
-      <c r="S2" t="n">
-        <v>359126071.84</v>
-      </c>
+        <v>-55000000</v>
+      </c>
+      <c r="S2" t="inlineStr"/>
       <c r="T2" t="n">
-        <v>-482746255.09</v>
+        <v>-55000000</v>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="inlineStr"/>
       <c r="W2" t="n">
-        <v>-1807947.99</v>
+        <v>-14015230.77</v>
       </c>
       <c r="X2" t="n">
-        <v>2600892.56</v>
+        <v>41048</v>
       </c>
       <c r="Y2" t="n">
-        <v>-4408840.55</v>
+        <v>-14056278.77</v>
       </c>
       <c r="Z2" t="n">
-        <v>-137724594</v>
+        <v>-2605343515.45</v>
       </c>
       <c r="AA2" t="n">
-        <v>-776570145.61</v>
+        <v>-3705817789.2</v>
       </c>
       <c r="AB2" t="n">
-        <v>-14585314.56</v>
+        <v>-17483467.54</v>
       </c>
       <c r="AC2" t="n">
-        <v>2425514598.75</v>
+        <v>243669229.28</v>
       </c>
       <c r="AD2" t="n">
-        <v>-863237695.35</v>
+        <v>-3384846622.05</v>
       </c>
       <c r="AE2" t="n">
-        <v>-2324261734.45</v>
+        <v>-547156928.89</v>
       </c>
       <c r="AF2" t="n">
-        <v>179613311.07</v>
+        <v>103588812.42</v>
       </c>
       <c r="AG2" t="n">
-        <v>77917320.40000001</v>
+        <v>38114253.65</v>
       </c>
       <c r="AH2" t="n">
-        <v>1618585.09</v>
+        <v>1152638.5</v>
       </c>
       <c r="AI2" t="n">
-        <v>76298735.31</v>
+        <v>36961615.15</v>
       </c>
       <c r="AJ2" t="n">
-        <v>2263764.08</v>
+        <v>-1265124.54</v>
       </c>
       <c r="AK2" t="n">
-        <v>-1594585.61</v>
+        <v>-545830.67</v>
       </c>
       <c r="AL2" t="n">
-        <v>95674050.42</v>
+        <v>900218647.17</v>
       </c>
       <c r="AM2" t="n">
-        <v>-137724594</v>
+        <v>-2605343515.45</v>
       </c>
       <c r="AN2" t="n">
-        <v>-837237846.09</v>
+        <v>-936956684.6799999</v>
       </c>
       <c r="AO2" t="n">
-        <v>-11370685254.22</v>
+        <v>-10008271122.21</v>
       </c>
       <c r="AP2" t="n">
-        <v>-835183277.39</v>
+        <v>-804102855.17</v>
       </c>
       <c r="AQ2" t="n">
-        <v>-220120241.96</v>
+        <v>-130649462.11</v>
       </c>
       <c r="AR2" t="n">
-        <v>-10315381734.87</v>
+        <v>-9073518804.93</v>
       </c>
       <c r="AS2" t="n">
-        <v>12070198506.31</v>
+        <v>8339884291.44</v>
       </c>
       <c r="AT2" t="n">
-        <v>1010903464.98</v>
+        <v>112192586.89</v>
       </c>
       <c r="AU2" t="n">
-        <v>11059295041.33</v>
+        <v>8227691704.55</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>1066797131.74</v>
+        <v>-1903987110.67</v>
       </c>
       <c r="C3" t="n">
-        <v>-4196029800</v>
+        <v>-1376875449.92</v>
       </c>
       <c r="D3" t="n">
-        <v>3361757585.11</v>
+        <v>7707684161.26</v>
       </c>
       <c r="E3" t="n">
-        <v>-14473772.17</v>
+        <v>-18573680.63</v>
       </c>
       <c r="F3" t="n">
-        <v>3745741027.91</v>
+        <v>4581833027.46</v>
       </c>
       <c r="G3" t="n">
-        <v>4581833027.46</v>
+        <v>2864715464.2</v>
       </c>
       <c r="H3" t="n">
-        <v>-836091999.55</v>
+        <v>1717117563.26</v>
       </c>
       <c r="I3" t="n">
-        <v>-1677129588.7</v>
+        <v>3575452560.86</v>
       </c>
       <c r="J3" t="n">
-        <v>-404628024.81</v>
+        <v>-2280623007.5</v>
       </c>
       <c r="K3" t="n">
-        <v>-438229349</v>
+        <v>-381402342.98</v>
       </c>
       <c r="L3" t="n">
-        <v>-834272214.89</v>
+        <v>6330808711.34</v>
       </c>
       <c r="M3" t="n">
-        <v>-834272214.89</v>
+        <v>6330808711.34</v>
       </c>
       <c r="N3" t="n">
-        <v>-4196029800</v>
+        <v>-1376875449.92</v>
       </c>
       <c r="O3" t="n">
-        <v>3361757585.11</v>
+        <v>7707684161.26</v>
       </c>
       <c r="P3" t="n">
-        <v>-240233314.76</v>
+        <v>27078432.44</v>
       </c>
       <c r="Q3" t="n">
-        <v>116473057.41</v>
+        <v>-2276950.02</v>
       </c>
       <c r="R3" t="n">
-        <v>-342250000</v>
-      </c>
-      <c r="S3" t="inlineStr"/>
+        <v>40000000</v>
+      </c>
+      <c r="S3" t="n">
+        <v>90000000</v>
+      </c>
       <c r="T3" t="n">
-        <v>-342250000</v>
+        <v>-50000000</v>
       </c>
       <c r="U3" t="n">
-        <v>17400</v>
+        <v>7929063.09</v>
       </c>
       <c r="V3" t="n">
-        <v>17400</v>
+        <v>7929063.09</v>
       </c>
       <c r="W3" t="n">
-        <v>-14456372.17</v>
+        <v>-18573680.63</v>
       </c>
       <c r="X3" t="n">
-        <v>17400</v>
+        <v>7929063.09</v>
       </c>
       <c r="Y3" t="n">
-        <v>-14473772.17</v>
+        <v>-18573680.63</v>
       </c>
       <c r="Z3" t="n">
-        <v>1081270903.91</v>
+        <v>-1885413430.04</v>
       </c>
       <c r="AA3" t="n">
-        <v>221565513.04</v>
+        <v>-2469378665.04</v>
       </c>
       <c r="AB3" t="n">
-        <v>-69670707.26000001</v>
+        <v>-42028102.26</v>
       </c>
       <c r="AC3" t="n">
-        <v>4085704653.12</v>
+        <v>5347541572.37</v>
       </c>
       <c r="AD3" t="n">
-        <v>-2093013111.5</v>
+        <v>-6630010651.36</v>
       </c>
       <c r="AE3" t="n">
-        <v>-1701455321.32</v>
+        <v>-1144881483.79</v>
       </c>
       <c r="AF3" t="n">
-        <v>57327545.54</v>
+        <v>135366061.65</v>
       </c>
       <c r="AG3" t="n">
-        <v>41978309.49</v>
+        <v>38742646.04</v>
       </c>
       <c r="AH3" t="n">
-        <v>1744072.31</v>
+        <v>1009164.18</v>
       </c>
       <c r="AI3" t="n">
-        <v>40234237.18</v>
+        <v>37733481.86</v>
       </c>
       <c r="AJ3" t="n">
-        <v>9858740.619999999</v>
+        <v>-44546003.3</v>
       </c>
       <c r="AK3" t="n">
-        <v>57296.65</v>
+        <v>-5389652.97</v>
       </c>
       <c r="AL3" t="n">
-        <v>398084041.53</v>
+        <v>403335592.04</v>
       </c>
       <c r="AM3" t="n">
-        <v>1081270903.91</v>
+        <v>-1885413430.04</v>
       </c>
       <c r="AN3" t="n">
-        <v>-1000087372.96</v>
+        <v>-1299452363.3</v>
       </c>
       <c r="AO3" t="n">
-        <v>-10601559782.69</v>
+        <v>-10087052599.47</v>
       </c>
       <c r="AP3" t="n">
-        <v>-1590944117.49</v>
+        <v>-670302814.03</v>
       </c>
       <c r="AQ3" t="n">
-        <v>-186422610.62</v>
+        <v>-158344390.96</v>
       </c>
       <c r="AR3" t="n">
-        <v>-8824193054.58</v>
+        <v>-9258405394.48</v>
       </c>
       <c r="AS3" t="n">
-        <v>12682918059.56</v>
+        <v>9501091532.73</v>
       </c>
       <c r="AT3" t="n">
-        <v>785737876.5700001</v>
+        <v>1147542934.48</v>
       </c>
       <c r="AU3" t="n">
-        <v>11897180182.99</v>
+        <v>8353548598.25</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>-1903987110.67</v>
+        <v>1066797131.74</v>
       </c>
       <c r="C4" t="n">
-        <v>-1376875449.92</v>
+        <v>-4196029800</v>
       </c>
       <c r="D4" t="n">
-        <v>7707684161.26</v>
+        <v>3361757585.11</v>
       </c>
       <c r="E4" t="n">
-        <v>-18573680.63</v>
+        <v>-14473772.17</v>
       </c>
       <c r="F4" t="n">
+        <v>3745741027.91</v>
+      </c>
+      <c r="G4" t="n">
         <v>4581833027.46</v>
       </c>
-      <c r="G4" t="n">
-        <v>2864715464.2</v>
-      </c>
       <c r="H4" t="n">
-        <v>1717117563.26</v>
+        <v>-836091999.55</v>
       </c>
       <c r="I4" t="n">
-        <v>3575452560.86</v>
+        <v>-1677129588.7</v>
       </c>
       <c r="J4" t="n">
-        <v>-2280623007.5</v>
+        <v>-404628024.81</v>
       </c>
       <c r="K4" t="n">
-        <v>-381402342.98</v>
+        <v>-438229349</v>
       </c>
       <c r="L4" t="n">
-        <v>6330808711.34</v>
+        <v>-834272214.89</v>
       </c>
       <c r="M4" t="n">
-        <v>6330808711.34</v>
+        <v>-834272214.89</v>
       </c>
       <c r="N4" t="n">
-        <v>-1376875449.92</v>
+        <v>-4196029800</v>
       </c>
       <c r="O4" t="n">
-        <v>7707684161.26</v>
+        <v>3361757585.11</v>
       </c>
       <c r="P4" t="n">
-        <v>27078432.44</v>
+        <v>-240233314.76</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2276950.02</v>
+        <v>116473057.41</v>
       </c>
       <c r="R4" t="n">
-        <v>40000000</v>
-      </c>
-      <c r="S4" t="n">
-        <v>90000000</v>
-      </c>
+        <v>-342250000</v>
+      </c>
+      <c r="S4" t="inlineStr"/>
       <c r="T4" t="n">
-        <v>-50000000</v>
+        <v>-342250000</v>
       </c>
       <c r="U4" t="n">
-        <v>7929063.09</v>
+        <v>17400</v>
       </c>
       <c r="V4" t="n">
-        <v>7929063.09</v>
+        <v>17400</v>
       </c>
       <c r="W4" t="n">
-        <v>-18573680.63</v>
+        <v>-14456372.17</v>
       </c>
       <c r="X4" t="n">
-        <v>7929063.09</v>
+        <v>17400</v>
       </c>
       <c r="Y4" t="n">
-        <v>-18573680.63</v>
+        <v>-14473772.17</v>
       </c>
       <c r="Z4" t="n">
-        <v>-1885413430.04</v>
+        <v>1081270903.91</v>
       </c>
       <c r="AA4" t="n">
-        <v>-2469378665.04</v>
+        <v>221565513.04</v>
       </c>
       <c r="AB4" t="n">
-        <v>-42028102.26</v>
+        <v>-69670707.26000001</v>
       </c>
       <c r="AC4" t="n">
-        <v>5347541572.37</v>
+        <v>4085704653.12</v>
       </c>
       <c r="AD4" t="n">
-        <v>-6630010651.36</v>
+        <v>-2093013111.5</v>
       </c>
       <c r="AE4" t="n">
-        <v>-1144881483.79</v>
+        <v>-1701455321.32</v>
       </c>
       <c r="AF4" t="n">
-        <v>135366061.65</v>
+        <v>57327545.54</v>
       </c>
       <c r="AG4" t="n">
-        <v>38742646.04</v>
+        <v>41978309.49</v>
       </c>
       <c r="AH4" t="n">
-        <v>1009164.18</v>
+        <v>1744072.31</v>
       </c>
       <c r="AI4" t="n">
-        <v>37733481.86</v>
+        <v>40234237.18</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-44546003.3</v>
+        <v>9858740.619999999</v>
       </c>
       <c r="AK4" t="n">
-        <v>-5389652.97</v>
+        <v>57296.65</v>
       </c>
       <c r="AL4" t="n">
-        <v>403335592.04</v>
+        <v>398084041.53</v>
       </c>
       <c r="AM4" t="n">
-        <v>-1885413430.04</v>
+        <v>1081270903.91</v>
       </c>
       <c r="AN4" t="n">
-        <v>-1299452363.3</v>
+        <v>-1000087372.96</v>
       </c>
       <c r="AO4" t="n">
-        <v>-10087052599.47</v>
+        <v>-10601559782.69</v>
       </c>
       <c r="AP4" t="n">
-        <v>-670302814.03</v>
+        <v>-1590944117.49</v>
       </c>
       <c r="AQ4" t="n">
-        <v>-158344390.96</v>
+        <v>-186422610.62</v>
       </c>
       <c r="AR4" t="n">
-        <v>-9258405394.48</v>
+        <v>-8824193054.58</v>
       </c>
       <c r="AS4" t="n">
-        <v>9501091532.73</v>
+        <v>12682918059.56</v>
       </c>
       <c r="AT4" t="n">
-        <v>1147542934.48</v>
+        <v>785737876.5700001</v>
       </c>
       <c r="AU4" t="n">
-        <v>8353548598.25</v>
+        <v>11897180182.99</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>-2619399794.22</v>
+        <v>-142133434.55</v>
       </c>
       <c r="C5" t="n">
-        <v>-2002233824.68</v>
+        <v>-4042921513.07</v>
       </c>
       <c r="D5" t="n">
-        <v>1989626375.5</v>
+        <v>5335007912.6</v>
       </c>
       <c r="E5" t="n">
-        <v>-14056278.77</v>
+        <v>-4408840.55</v>
       </c>
       <c r="F5" t="n">
-        <v>2864715464.2</v>
+        <v>5240479717.74</v>
       </c>
       <c r="G5" t="n">
-        <v>3170244377.7</v>
+        <v>3745741027.91</v>
       </c>
       <c r="H5" t="n">
-        <v>-305528913.5</v>
+        <v>1494738689.83</v>
       </c>
       <c r="I5" t="n">
-        <v>2476093066.69</v>
+        <v>2153660056.15</v>
       </c>
       <c r="J5" t="n">
-        <v>2828542708.5</v>
+        <v>1343693831.47</v>
       </c>
       <c r="K5" t="n">
-        <v>-339842192.63</v>
+        <v>-398120174.85</v>
       </c>
       <c r="L5" t="n">
-        <v>-12607449.18</v>
+        <v>1292086399.53</v>
       </c>
       <c r="M5" t="n">
-        <v>-12607449.18</v>
+        <v>1292086399.53</v>
       </c>
       <c r="N5" t="n">
-        <v>-2002233824.68</v>
+        <v>-4042921513.07</v>
       </c>
       <c r="O5" t="n">
-        <v>1989626375.5</v>
+        <v>5335007912.6</v>
       </c>
       <c r="P5" t="n">
-        <v>-176278464.74</v>
+        <v>-521196772.32</v>
       </c>
       <c r="Q5" t="n">
-        <v>-107263233.97</v>
+        <v>-395768641.08</v>
       </c>
       <c r="R5" t="n">
-        <v>-55000000</v>
-      </c>
-      <c r="S5" t="inlineStr"/>
+        <v>-123620183.25</v>
+      </c>
+      <c r="S5" t="n">
+        <v>359126071.84</v>
+      </c>
       <c r="T5" t="n">
-        <v>-55000000</v>
+        <v>-482746255.09</v>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>-14015230.77</v>
+        <v>-1807947.99</v>
       </c>
       <c r="X5" t="n">
-        <v>41048</v>
+        <v>2600892.56</v>
       </c>
       <c r="Y5" t="n">
-        <v>-14056278.77</v>
+        <v>-4408840.55</v>
       </c>
       <c r="Z5" t="n">
-        <v>-2605343515.45</v>
+        <v>-137724594</v>
       </c>
       <c r="AA5" t="n">
-        <v>-3705817789.2</v>
+        <v>-776570145.61</v>
       </c>
       <c r="AB5" t="n">
-        <v>-17483467.54</v>
+        <v>-14585314.56</v>
       </c>
       <c r="AC5" t="n">
-        <v>243669229.28</v>
+        <v>2425514598.75</v>
       </c>
       <c r="AD5" t="n">
-        <v>-3384846622.05</v>
+        <v>-863237695.35</v>
       </c>
       <c r="AE5" t="n">
-        <v>-547156928.89</v>
+        <v>-2324261734.45</v>
       </c>
       <c r="AF5" t="n">
-        <v>103588812.42</v>
+        <v>179613311.07</v>
       </c>
       <c r="AG5" t="n">
-        <v>38114253.65</v>
+        <v>77917320.40000001</v>
       </c>
       <c r="AH5" t="n">
-        <v>1152638.5</v>
+        <v>1618585.09</v>
       </c>
       <c r="AI5" t="n">
-        <v>36961615.15</v>
+        <v>76298735.31</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-1265124.54</v>
+        <v>2263764.08</v>
       </c>
       <c r="AK5" t="n">
-        <v>-545830.67</v>
+        <v>-1594585.61</v>
       </c>
       <c r="AL5" t="n">
-        <v>900218647.17</v>
+        <v>95674050.42</v>
       </c>
       <c r="AM5" t="n">
-        <v>-2605343515.45</v>
+        <v>-137724594</v>
       </c>
       <c r="AN5" t="n">
-        <v>-936956684.6799999</v>
+        <v>-837237846.09</v>
       </c>
       <c r="AO5" t="n">
-        <v>-10008271122.21</v>
+        <v>-11370685254.22</v>
       </c>
       <c r="AP5" t="n">
-        <v>-804102855.17</v>
+        <v>-835183277.39</v>
       </c>
       <c r="AQ5" t="n">
-        <v>-130649462.11</v>
+        <v>-220120241.96</v>
       </c>
       <c r="AR5" t="n">
-        <v>-9073518804.93</v>
+        <v>-10315381734.87</v>
       </c>
       <c r="AS5" t="n">
-        <v>8339884291.44</v>
+        <v>12070198506.31</v>
       </c>
       <c r="AT5" t="n">
-        <v>112192586.89</v>
+        <v>1010903464.98</v>
       </c>
       <c r="AU5" t="n">
-        <v>8227691704.55</v>
+        <v>11059295041.33</v>
       </c>
     </row>
   </sheetData>
@@ -3868,172 +3868,172 @@
       </c>
       <c r="DD1" t="inlineStr">
         <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="DE1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="DF1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="DG1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="DH1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="DI1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChangePercent</t>
+        </is>
+      </c>
+      <c r="DJ1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekRange</t>
+        </is>
+      </c>
+      <c r="DK1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChange</t>
+        </is>
+      </c>
+      <c r="DL1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChangePercent</t>
+        </is>
+      </c>
+      <c r="DM1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekChangePercent</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
+        <is>
+          <t>earningsTimestampStart</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>earningsTimestampEnd</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>epsTrailingTwelveMonths</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChange</t>
+        </is>
+      </c>
+      <c r="DR1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChange</t>
+        </is>
+      </c>
+      <c r="DT1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="DU1" t="inlineStr">
+        <is>
+          <t>sourceInterval</t>
+        </is>
+      </c>
+      <c r="DV1" t="inlineStr">
+        <is>
+          <t>exchangeDataDelayedBy</t>
+        </is>
+      </c>
+      <c r="DW1" t="inlineStr">
+        <is>
+          <t>shortName</t>
+        </is>
+      </c>
+      <c r="DX1" t="inlineStr">
+        <is>
+          <t>longName</t>
+        </is>
+      </c>
+      <c r="DY1" t="inlineStr">
+        <is>
+          <t>cryptoTradeable</t>
+        </is>
+      </c>
+      <c r="DZ1" t="inlineStr">
+        <is>
           <t>marketState</t>
         </is>
       </c>
-      <c r="DE1" t="inlineStr">
+      <c r="EA1" t="inlineStr">
+        <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="EB1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="EC1" t="inlineStr">
+        <is>
+          <t>corporateActions</t>
+        </is>
+      </c>
+      <c r="ED1" t="inlineStr">
+        <is>
+          <t>regularMarketTime</t>
+        </is>
+      </c>
+      <c r="EE1" t="inlineStr">
+        <is>
+          <t>exchange</t>
+        </is>
+      </c>
+      <c r="EF1" t="inlineStr">
         <is>
           <t>messageBoardId</t>
         </is>
       </c>
-      <c r="DF1" t="inlineStr">
+      <c r="EG1" t="inlineStr">
         <is>
           <t>exchangeTimezoneName</t>
         </is>
       </c>
-      <c r="DG1" t="inlineStr">
+      <c r="EH1" t="inlineStr">
         <is>
           <t>exchangeTimezoneShortName</t>
         </is>
       </c>
-      <c r="DH1" t="inlineStr">
+      <c r="EI1" t="inlineStr">
         <is>
           <t>gmtOffSetMilliseconds</t>
         </is>
       </c>
-      <c r="DI1" t="inlineStr">
+      <c r="EJ1" t="inlineStr">
         <is>
           <t>market</t>
         </is>
       </c>
-      <c r="DJ1" t="inlineStr">
+      <c r="EK1" t="inlineStr">
         <is>
           <t>esgPopulated</t>
-        </is>
-      </c>
-      <c r="DK1" t="inlineStr">
-        <is>
-          <t>shortName</t>
-        </is>
-      </c>
-      <c r="DL1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChange</t>
-        </is>
-      </c>
-      <c r="DM1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="DN1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
-      <c r="DO1" t="inlineStr">
-        <is>
-          <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
-      <c r="DP1" t="inlineStr">
-        <is>
-          <t>cryptoTradeable</t>
-        </is>
-      </c>
-      <c r="DQ1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="DR1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="DS1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="DT1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
-        </is>
-      </c>
-      <c r="DU1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="DV1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="DW1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="DX1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChangePercent</t>
-        </is>
-      </c>
-      <c r="DY1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekRange</t>
-        </is>
-      </c>
-      <c r="DZ1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChange</t>
-        </is>
-      </c>
-      <c r="EA1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChangePercent</t>
-        </is>
-      </c>
-      <c r="EB1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekChangePercent</t>
-        </is>
-      </c>
-      <c r="EC1" t="inlineStr">
-        <is>
-          <t>earningsTimestampStart</t>
-        </is>
-      </c>
-      <c r="ED1" t="inlineStr">
-        <is>
-          <t>earningsTimestampEnd</t>
-        </is>
-      </c>
-      <c r="EE1" t="inlineStr">
-        <is>
-          <t>epsTrailingTwelveMonths</t>
-        </is>
-      </c>
-      <c r="EF1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChange</t>
-        </is>
-      </c>
-      <c r="EG1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="EH1" t="inlineStr">
-        <is>
-          <t>corporateActions</t>
-        </is>
-      </c>
-      <c r="EI1" t="inlineStr">
-        <is>
-          <t>regularMarketTime</t>
-        </is>
-      </c>
-      <c r="EJ1" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="EK1" t="inlineStr">
-        <is>
-          <t>longName</t>
         </is>
       </c>
       <c r="EL1" t="inlineStr">
@@ -4138,28 +4138,28 @@
         <v>2</v>
       </c>
       <c r="U2" t="n">
-        <v>17.8</v>
+        <v>18.77</v>
       </c>
       <c r="V2" t="n">
-        <v>22.44</v>
+        <v>17.31</v>
       </c>
       <c r="W2" t="n">
-        <v>16.93</v>
+        <v>17.99</v>
       </c>
       <c r="X2" t="n">
-        <v>17.98</v>
+        <v>19.63</v>
       </c>
       <c r="Y2" t="n">
-        <v>17.8</v>
+        <v>18.77</v>
       </c>
       <c r="Z2" t="n">
-        <v>22.44</v>
+        <v>17.31</v>
       </c>
       <c r="AA2" t="n">
-        <v>16.93</v>
+        <v>17.99</v>
       </c>
       <c r="AB2" t="n">
-        <v>17.98</v>
+        <v>19.63</v>
       </c>
       <c r="AC2" t="n">
         <v>1721088000</v>
@@ -4171,28 +4171,28 @@
         <v>1.09</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.312</v>
+        <v>1.369</v>
       </c>
       <c r="AG2" t="n">
-        <v>76641542</v>
+        <v>109287920</v>
       </c>
       <c r="AH2" t="n">
-        <v>76641542</v>
+        <v>109287920</v>
       </c>
       <c r="AI2" t="n">
-        <v>56889546</v>
+        <v>61501455</v>
       </c>
       <c r="AJ2" t="n">
-        <v>119899019</v>
+        <v>71947099</v>
       </c>
       <c r="AK2" t="n">
-        <v>119899019</v>
+        <v>71947099</v>
       </c>
       <c r="AL2" t="n">
-        <v>17.02</v>
+        <v>18.18</v>
       </c>
       <c r="AM2" t="n">
-        <v>17.03</v>
+        <v>18.19</v>
       </c>
       <c r="AN2" t="n">
         <v>0</v>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>13704159232</v>
+        <v>14603846656</v>
       </c>
       <c r="AQ2" t="n">
-        <v>13704159711</v>
+        <v>15077788850</v>
       </c>
       <c r="AR2" t="n">
-        <v>6.22</v>
+        <v>6.38</v>
       </c>
       <c r="AS2" t="n">
         <v>26.36</v>
@@ -4219,13 +4219,13 @@
         <v>1.734615</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.2670684</v>
+        <v>1.3502523</v>
       </c>
       <c r="AW2" t="n">
-        <v>14.9132</v>
+        <v>16.1154</v>
       </c>
       <c r="AX2" t="n">
-        <v>12.60365</v>
+        <v>13.28625</v>
       </c>
       <c r="AY2" t="n">
         <v>0</v>
@@ -4242,13 +4242,13 @@
         <v>0</v>
       </c>
       <c r="BC2" t="n">
-        <v>26786027520</v>
+        <v>27685713920</v>
       </c>
       <c r="BD2" t="n">
         <v>-0.05129</v>
       </c>
       <c r="BE2" t="n">
-        <v>323300889</v>
+        <v>323292856</v>
       </c>
       <c r="BF2" t="n">
         <v>803291894</v>
@@ -4266,7 +4266,7 @@
         <v>7.373</v>
       </c>
       <c r="BK2" t="n">
-        <v>2.3138478</v>
+        <v>2.4657533</v>
       </c>
       <c r="BL2" t="n">
         <v>1767139200</v>
@@ -4292,16 +4292,16 @@
         <v>1557792000</v>
       </c>
       <c r="BS2" t="n">
-        <v>2.477</v>
+        <v>2.56</v>
       </c>
       <c r="BT2" t="n">
-        <v>59.146</v>
+        <v>61.133</v>
       </c>
       <c r="BU2" t="n">
-        <v>1.6367853</v>
+        <v>1.7242379</v>
       </c>
       <c r="BV2" t="n">
-        <v>0.27697718</v>
+        <v>0.24487448</v>
       </c>
       <c r="BW2" t="n">
         <v>0.08500000000000001</v>
@@ -4315,7 +4315,7 @@
         </is>
       </c>
       <c r="BZ2" t="n">
-        <v>17.06</v>
+        <v>18.18</v>
       </c>
       <c r="CA2" t="inlineStr">
         <is>
@@ -4415,136 +4415,136 @@
         </is>
       </c>
       <c r="DB2" t="n">
-        <v>-4.1573024</v>
+        <v>-3.1433146</v>
       </c>
       <c r="DC2" t="n">
-        <v>17.06</v>
-      </c>
-      <c r="DD2" t="inlineStr">
-        <is>
-          <t>CLOSED</t>
-        </is>
+        <v>18.18</v>
+      </c>
+      <c r="DD2" t="n">
+        <v>-0.5900001499999999</v>
       </c>
       <c r="DE2" t="inlineStr">
         <is>
+          <t>17.99 - 19.63</t>
+        </is>
+      </c>
+      <c r="DF2" t="inlineStr">
+        <is>
+          <t>Shenzhen</t>
+        </is>
+      </c>
+      <c r="DG2" t="n">
+        <v>61501455</v>
+      </c>
+      <c r="DH2" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="DI2" t="n">
+        <v>1.8495297</v>
+      </c>
+      <c r="DJ2" t="inlineStr">
+        <is>
+          <t>6.38 - 26.36</t>
+        </is>
+      </c>
+      <c r="DK2" t="n">
+        <v>-8.18</v>
+      </c>
+      <c r="DL2" t="n">
+        <v>-0.31031868</v>
+      </c>
+      <c r="DM2" t="n">
+        <v>172.4238</v>
+      </c>
+      <c r="DN2" t="n">
+        <v>1619521140</v>
+      </c>
+      <c r="DO2" t="n">
+        <v>1619521140</v>
+      </c>
+      <c r="DP2" t="n">
+        <v>-0.6899999999999999</v>
+      </c>
+      <c r="DQ2" t="n">
+        <v>2.0646</v>
+      </c>
+      <c r="DR2" t="n">
+        <v>0.12811348</v>
+      </c>
+      <c r="DS2" t="n">
+        <v>4.89375</v>
+      </c>
+      <c r="DT2" t="n">
+        <v>0.36833194</v>
+      </c>
+      <c r="DU2" t="n">
+        <v>15</v>
+      </c>
+      <c r="DV2" t="n">
+        <v>15</v>
+      </c>
+      <c r="DW2" t="inlineStr">
+        <is>
+          <t>HEFEI URBAN CONSTRUCTION DEVELO</t>
+        </is>
+      </c>
+      <c r="DX2" t="inlineStr">
+        <is>
+          <t>Hefei Urban Construction Development Co., Ltd</t>
+        </is>
+      </c>
+      <c r="DY2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DZ2" t="inlineStr">
+        <is>
+          <t>PREPRE</t>
+        </is>
+      </c>
+      <c r="EA2" t="b">
+        <v>0</v>
+      </c>
+      <c r="EB2" t="n">
+        <v>1201483800000</v>
+      </c>
+      <c r="EC2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="ED2" t="n">
+        <v>1782111894</v>
+      </c>
+      <c r="EE2" t="inlineStr">
+        <is>
+          <t>SHZ</t>
+        </is>
+      </c>
+      <c r="EF2" t="inlineStr">
+        <is>
           <t>finmb_32569824</t>
         </is>
       </c>
-      <c r="DF2" t="inlineStr">
+      <c r="EG2" t="inlineStr">
         <is>
           <t>Asia/Shanghai</t>
         </is>
       </c>
-      <c r="DG2" t="inlineStr">
+      <c r="EH2" t="inlineStr">
         <is>
           <t>CST</t>
         </is>
       </c>
-      <c r="DH2" t="n">
+      <c r="EI2" t="n">
         <v>28800000</v>
       </c>
-      <c r="DI2" t="inlineStr">
+      <c r="EJ2" t="inlineStr">
         <is>
           <t>cn_market</t>
         </is>
       </c>
-      <c r="DJ2" t="b">
+      <c r="EK2" t="b">
         <v>0</v>
-      </c>
-      <c r="DK2" t="inlineStr">
-        <is>
-          <t>HEFEI URBAN CONSTRUCTION DEVELO</t>
-        </is>
-      </c>
-      <c r="DL2" t="n">
-        <v>4.4563494</v>
-      </c>
-      <c r="DM2" t="n">
-        <v>0.3535761</v>
-      </c>
-      <c r="DN2" t="n">
-        <v>15</v>
-      </c>
-      <c r="DO2" t="n">
-        <v>15</v>
-      </c>
-      <c r="DP2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DQ2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DR2" t="n">
-        <v>1201483800000</v>
-      </c>
-      <c r="DS2" t="n">
-        <v>-0.7399998</v>
-      </c>
-      <c r="DT2" t="inlineStr">
-        <is>
-          <t>16.93 - 17.98</t>
-        </is>
-      </c>
-      <c r="DU2" t="inlineStr">
-        <is>
-          <t>Shenzhen</t>
-        </is>
-      </c>
-      <c r="DV2" t="n">
-        <v>56889546</v>
-      </c>
-      <c r="DW2" t="n">
-        <v>10.84</v>
-      </c>
-      <c r="DX2" t="n">
-        <v>1.7427653</v>
-      </c>
-      <c r="DY2" t="inlineStr">
-        <is>
-          <t>6.22 - 26.36</t>
-        </is>
-      </c>
-      <c r="DZ2" t="n">
-        <v>-9.300001</v>
-      </c>
-      <c r="EA2" t="n">
-        <v>-0.3528073</v>
-      </c>
-      <c r="EB2" t="n">
-        <v>163.67853</v>
-      </c>
-      <c r="EC2" t="n">
-        <v>1619521140</v>
-      </c>
-      <c r="ED2" t="n">
-        <v>1619521140</v>
-      </c>
-      <c r="EE2" t="n">
-        <v>-0.6899999999999999</v>
-      </c>
-      <c r="EF2" t="n">
-        <v>2.146799</v>
-      </c>
-      <c r="EG2" t="n">
-        <v>0.14395294</v>
-      </c>
-      <c r="EH2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="EI2" t="n">
-        <v>1780038246</v>
-      </c>
-      <c r="EJ2" t="inlineStr">
-        <is>
-          <t>SHZ</t>
-        </is>
-      </c>
-      <c r="EK2" t="inlineStr">
-        <is>
-          <t>Hefei Urban Construction Development Co., Ltd</t>
-        </is>
       </c>
       <c r="EL2" t="inlineStr"/>
     </row>
